--- a/practice/answers/s1_q18.xlsx
+++ b/practice/answers/s1_q18.xlsx
@@ -548,11 +548,11 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Larch</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>41.2</v>
+        <v>43.6</v>
       </c>
       <c r="C7" s="9">
         <f>IF(B7&gt;$B$4,"Above","Below")</f>
@@ -566,11 +566,11 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>38.6</v>
+        <v>37.9</v>
       </c>
       <c r="C8" s="9">
         <f>IF(B8&gt;$B$4,"Above","Below")</f>
@@ -584,11 +584,11 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Creek</t>
+          <t>Nordegg</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>44.8</v>
+        <v>51.4</v>
       </c>
       <c r="C9" s="9">
         <f>IF(B9&gt;$B$4,"Above","Below")</f>
@@ -602,11 +602,11 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Pothole</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>36.1</v>
+        <v>35.2</v>
       </c>
       <c r="C10" s="9">
         <f>IF(B10&gt;$B$4,"Above","Below")</f>
@@ -620,11 +620,11 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Rented</t>
+          <t>Ridgeway</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>39.9</v>
+        <v>40.8</v>
       </c>
       <c r="C11" s="9">
         <f>IF(B11&gt;$B$4,"Above","Below")</f>
@@ -655,7 +655,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Two of five, because Creek's 44.8 pulls the average up above three of the other four. An average is not a midpoint. Drop the $ signs and the reference slides down with the fill, so by the last row it compares against an empty cell -- which Excel reads as 0, and every yield beats 0.</t>
+          <t>Two of five, because Nordegg's 51.4 pulls the average up above three of the other four. An average is not a midpoint. Drop the $ signs and the reference slides down with the fill, so by the last row it compares against an empty cell -- which Excel reads as 0, and every yield beats 0.</t>
         </is>
       </c>
     </row>

--- a/practice/answers/s1_q18.xlsx
+++ b/practice/answers/s1_q18.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,45 +28,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +40,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,32 +76,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,183 +458,217 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Comparing each row against one cell</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>The average lives in a cell and the IF column points at it with an absolute reference. Without the $ the comparison walks off the end of the data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Farm average</t>
-        </is>
-      </c>
-      <c r="B4" s="4">
-        <f>AVERAGE(B7:B11)</f>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Yield (bu/ac)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Vs average</t>
+        </is>
+      </c>
+      <c r="D1" s="3">
+        <f>AVERAGE(B2:B6)</f>
         <v/>
       </c>
-    </row>
-    <row r="5" ht="18" customHeight="1"/>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Yield (bu/ac)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Vs average</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>The formula in C</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Farm average (bu/ac)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Larch</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B2" s="5" t="n">
         <v>43.6</v>
       </c>
-      <c r="C7" s="9">
-        <f>IF(B7&gt;$B$4,"Above","Below")</f>
+      <c r="C2" s="6">
+        <f>IF(B2&gt;$D$1,"Above","Below")</f>
         <v/>
       </c>
-      <c r="D7" s="10">
-        <f>_xlfn.FORMULATEXT(C7)</f>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Marsh</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="C3" s="6">
+        <f>IF(B3&gt;$D$1,"Above","Below")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nordegg</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="C4" s="6">
+        <f>IF(B4&gt;$D$1,"Above","Below")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Pothole</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="C5" s="6">
+        <f>IF(B5&gt;$D$1,"Above","Below")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ridgeway</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="C6" s="6">
+        <f>IF(B6&gt;$D$1,"Above","Below")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Marsh</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="C8" s="9">
-        <f>IF(B8&gt;$B$4,"Above","Below")</f>
+          <t>Fields above average</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <f>COUNTIF(C2:C6,"Above")</f>
         <v/>
       </c>
-      <c r="D8" s="10">
-        <f>_xlfn.FORMULATEXT(C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Nordegg</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="C9" s="9">
-        <f>IF(B9&gt;$B$4,"Above","Below")</f>
-        <v/>
-      </c>
-      <c r="D9" s="10">
-        <f>_xlfn.FORMULATEXT(C9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Pothole</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="C10" s="9">
-        <f>IF(B10&gt;$B$4,"Above","Below")</f>
-        <v/>
-      </c>
-      <c r="D10" s="10">
-        <f>_xlfn.FORMULATEXT(C10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Ridgeway</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="C11" s="9">
-        <f>IF(B11&gt;$B$4,"Above","Below")</f>
-        <v/>
-      </c>
-      <c r="D11" s="10">
-        <f>_xlfn.FORMULATEXT(C11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1"/>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Fields above average</t>
-        </is>
-      </c>
-      <c r="C13" s="11">
-        <f>COUNTIF(C7:C11,"Above")</f>
-        <v/>
-      </c>
-      <c r="D13" s="10">
-        <f>_xlfn.FORMULATEXT(C13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1"/>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Two of five, because Nordegg's 51.4 pulls the average up above three of the other four. An average is not a midpoint. Drop the $ signs and the reference slides down with the fill, so by the last row it compares against an empty cell -- which Excel reads as 0, and every yield beats 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>The average is pulled up by Nordegg's 51.4, which sits well above the rest. An average is not a midpoint -- it can land above most of the values when one value is high.</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Without the $ the reference walks down with the formula, so by the last row it is comparing the yield against an empty cell, which Excel reads as 0 -- and every yield beats 0.</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A10:G11"/>
+    <mergeCell ref="A13:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
